--- a/src/main/resources/python/MultifacetedModeling/Results/OnAllTrain/DataDrivenNCOR/correlation-values.xlsx
+++ b/src/main/resources/python/MultifacetedModeling/Results/OnAllTrain/DataDrivenNCOR/correlation-values.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -45,15 +45,15 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -417,7 +417,7 @@
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -460,7 +460,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.954635299543599</t>
+          <t>0.6522616176757565</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7148881462351875</t>
+          <t>0.31952504021955835</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.9983636725938129</t>
+          <t>0.9940302114769562</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.19755785170995915</t>
+          <t>0.1689761962466143</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.24078738652843237</t>
+          <t>0.2167405958676676</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.37413280322597214</t>
+          <t>0.3145560626667078</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.24078738652843237</t>
+          <t>0.2167405958676676</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.5756676449959574</t>
+          <t>0.3546907615817759</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.3826521727059141</t>
+          <t>0.3018784159673046</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.2541833949159426</t>
+          <t>0.2167405958676676</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.4519498145020462</t>
+          <t>0.36864158167378575</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.3350668046817207</t>
+          <t>0.4355303486371656</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.24078738652843237</t>
+          <t>0.2167405958676676</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.53590948770304</t>
+          <t>0.6336270554311803</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.6292271769356287</t>
+          <t>0.2536032983213541</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.6292271769356287</t>
+          <t>0.2536032983213541</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.5428479137837365</t>
+          <t>0.2818864170755215</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.6292271769356287</t>
+          <t>0.2536032983213541</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.5055108718194654</t>
+          <t>0.28012336271119354</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.5428479137837365</t>
+          <t>0.2818864170755215</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.6225509733003604</t>
+          <t>0.2536032983213541</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.5199595912367255</t>
+          <t>0.2925650337663095</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.5801787489488576</t>
+          <t>0.24744346759364808</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.6041184781729549</t>
+          <t>0.2536032983213541</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.5801787489488576</t>
+          <t>0.24744346759364808</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.7642039498928618</t>
+          <t>0.5349454173810527</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.3825860929196666</t>
+          <t>0.3604156943164474</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.5715432459888516</t>
+          <t>0.3604156943164474</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.5105544535606018</t>
+          <t>0.3723340295057685</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.414448847476798</t>
+          <t>0.19904758076872983</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.522809933503755</t>
+          <t>0.30145156571587917</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.47017739160776706</t>
+          <t>0.27726661227772115</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.39178274164832066</t>
+          <t>0.4572810028076522</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.45789407293545287</t>
+          <t>0.29331429541342063</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.39856457674055584</t>
+          <t>0.38056973600463745</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.49886223957897563</t>
+          <t>0.4572810028076522</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.4168889417390537</t>
+          <t>0.4572810028076522</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.9983636725938129</t>
+          <t>0.8766703832751865</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.8165219710173579</t>
+          <t>0.6226657212700845</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.7148881462351875</t>
+          <t>0.31952504021955835</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.9983636725938129</t>
+          <t>0.7265351405159212</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.19755785170995915</t>
+          <t>0.1689761962466143</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.6041184781729549</t>
+          <t>0.31952504021955835</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.2900351930497638</t>
+          <t>0.3679194155307133</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0.5000866997699275</t>
+          <t>0.17126838686467669</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.9999999999999996</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>0.5127031746288467</t>
+          <t>0.20821927809462978</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0.5163188697194604</t>
+          <t>0.21338588269461006</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0.4197260752731704</t>
+          <t>0.32957831298534296</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0.5163188697194604</t>
+          <t>0.22312933386494282</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0.5561009994387924</t>
+          <t>0.3843388369756343</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0.4409754795801024</t>
+          <t>0.2666175313645691</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>0.5163188697194604</t>
+          <t>0.21338588269461006</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>0.5295962972898471</t>
+          <t>0.41431070670777903</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0.6328295080933338</t>
+          <t>0.5383748690806268</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0.5163188697194604</t>
+          <t>0.2418171279223289</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>0.7149571010081249</t>
+          <t>0.7387588286838627</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0.32564989166487246</t>
+          <t>0.17289722331263163</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0.32564989166487246</t>
+          <t>0.17289722331263163</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0.35720777580559815</t>
+          <t>0.18950680166072997</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0.32564989166487246</t>
+          <t>0.17289722331263163</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0.3533073989093317</t>
+          <t>0.2504968718733361</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>0.35720777580559815</t>
+          <t>0.18950680166072997</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>0.32564989166487246</t>
+          <t>0.17289722331263163</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>0.28670141798710524</t>
+          <t>0.2504968718733359</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>0.42861520040417705</t>
+          <t>0.20973176164850046</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>0.32564989166487246</t>
+          <t>0.17289722331263163</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>0.42861520040417705</t>
+          <t>0.20973176164850046</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>0.8522503803609405</t>
+          <t>0.6994009976324005</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0.4046559786742157</t>
+          <t>0.4116155964952706</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0.6740007859924494</t>
+          <t>0.32264242985858177</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>0.6352368632199117</t>
+          <t>0.46463880296757815</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0.312751636562777</t>
+          <t>0.26839956025559814</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0.6152363949742523</t>
+          <t>0.30599596405456486</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.3953724234608747</t>
+          <t>0.30022162700157</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>0.3465610009379516</t>
+          <t>0.32695151747350887</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.34630002694291867</t>
+          <t>0.273996527003441</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>0.4013447160560791</t>
+          <t>0.268976389848479</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.4668793385600661</t>
+          <t>0.2506559454572714</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.4266933510580405</t>
+          <t>0.29348509370644144</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>0.954635299543599</t>
+          <t>0.6522616176757565</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.998509098917632</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0.5000866997699275</t>
+          <t>0.17126838686467669</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.8733685971657758</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>0.5127031746288467</t>
+          <t>0.20821927809462978</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0.32564989166487246</t>
+          <t>0.17289722331263163</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>0.28665606943615307</t>
+          <t>0.3104255611108516</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>0.47303215618255384</t>
+          <t>0.26336749427691036</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>0.20894377738414507</t>
+          <t>0.16247513098660024</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>0.15357320137094524</t>
+          <t>0.12659394132512167</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>0.3353966885149807</t>
+          <t>0.1893738335189246</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>0.15357320137094524</t>
+          <t>0.12659394132512167</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>0.43364136066036635</t>
+          <t>0.20788923839145598</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>0.32450509286699825</t>
+          <t>0.17944273564211338</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>0.15357320137094524</t>
+          <t>0.12659394132512167</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>0.3769409211823908</t>
+          <t>0.22465402888199132</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>0.1627155831712404</t>
+          <t>0.15804315012487277</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>0.15357320137094524</t>
+          <t>0.12659394132512167</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>0.1587729291109816</t>
+          <t>0.15804315012487277</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>0.7082119425999194</t>
+          <t>0.529181152383134</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>0.7082119425999194</t>
+          <t>0.529181152383134</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>0.4931285322331685</t>
+          <t>0.38347323256637567</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>0.6629562793532694</t>
+          <t>0.5746356978376793</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>0.7116109233184235</t>
+          <t>0.3932954903110028</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>0.484429617863956</t>
+          <t>0.42713058429965534</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>0.6261563939499927</t>
+          <t>0.5746356978376793</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0.6157086379221312</t>
+          <t>0.5008831410686673</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>0.5368569052833821</t>
+          <t>0.42892777802092086</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>0.5699480893391555</t>
+          <t>0.4813922218413367</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>0.7092898346710996</t>
+          <t>0.48324007379100997</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>0.7138672085502374</t>
+          <t>0.3313570592086957</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>0.4174525357228982</t>
+          <t>0.39404244146696793</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>0.6154587809277017</t>
+          <t>0.3379380763696062</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>0.5487083623079247</t>
+          <t>0.36315200507917744</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>0.3996024176010812</t>
+          <t>0.2165673556346486</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>0.5483399343392193</t>
+          <t>0.4394969869215132</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>0.7029155270281294</t>
+          <t>0.34985949680363276</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>0.4929324319859154</t>
+          <t>0.3294822933436382</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>0.40733046544895657</t>
+          <t>0.4394969869215132</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>0.4774785046410294</t>
+          <t>0.4114596884731822</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>0.5126525674649292</t>
+          <t>0.4442970393380977</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>0.5317930024070758</t>
+          <t>0.3836227252527314</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>0.7148881462351875</t>
+          <t>0.36004976667337935</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>0.48289161707715866</t>
+          <t>0.19320106163716755</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>0.8175072881213616</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>0.8175072881213616</t>
+          <t>0.4808797773934798</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>0.20894377738414507</t>
+          <t>0.14334637218747343</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>0.663963071979175</t>
+          <t>0.529181152383134</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>0.2644358860625594</t>
+          <t>0.2725390430958687</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>0.5309036418355016</t>
+          <t>0.3099682900793622</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>0.5731149228243761</t>
+          <t>0.3020253038284767</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0.46540241086425993</t>
+          <t>0.27177627318258085</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>0.5731149228243761</t>
+          <t>0.3020253038284767</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>0.5561009994387924</t>
+          <t>0.3920988458459991</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>0.4409754795801024</t>
+          <t>0.39229645271579855</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>0.5731149228243761</t>
+          <t>0.3020253038284767</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>0.5295962972898471</t>
+          <t>0.39689999617541916</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>0.5562130522802231</t>
+          <t>0.6031308928750815</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>0.5731149228243761</t>
+          <t>0.3020253038284767</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>0.8035558981254178</t>
+          <t>0.7995343829593714</t>
         </is>
       </c>
     </row>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>0.4020243453491797</t>
+          <t>0.20993903421924998</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>0.40202434534917986</t>
+          <t>0.20993903421924998</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>0.47351647510556333</t>
+          <t>0.2689324695824415</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>0.40202434534917986</t>
+          <t>0.20993903421924998</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>0.43521980311057235</t>
+          <t>0.2835150956812861</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>0.47351647510556333</t>
+          <t>0.2256432161725029</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>0.40202434534917986</t>
+          <t>0.20993903421924998</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>0.4019766279155936</t>
+          <t>0.25049687187333625</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>0.5569250239305233</t>
+          <t>0.3341147750510366</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>0.40202434534917986</t>
+          <t>0.20993903421924998</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>0.5569250239305233</t>
+          <t>0.3341147750510366</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>0.8522503803609405</t>
+          <t>0.7785191679211588</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>0.4046559786742157</t>
+          <t>0.4384753389816341</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>0.6740007859924494</t>
+          <t>0.34538432103755584</t>
         </is>
       </c>
     </row>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>0.6352368632199117</t>
+          <t>0.5754236111929583</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>0.47811066052432094</t>
+          <t>0.38853772297968137</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>0.6152363949742523</t>
+          <t>0.40961937876085813</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>0.4177064679007876</t>
+          <t>0.25182535139672657</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>0.4042945609881804</t>
+          <t>0.29300979179025466</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>0.34747679215832034</t>
+          <t>0.2772666122777213</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>0.4042945609881804</t>
+          <t>0.3320588436184036</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>0.4668793385600661</t>
+          <t>0.29300979179025466</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>0.4266933510580405</t>
+          <t>0.29300979179025466</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>0.9983636725938129</t>
+          <t>0.785361525132805</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>0.9560898739101291</t>
+          <t>0.8955698940771588</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>0.47303215618255384</t>
+          <t>0.26336749427691036</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.8666175060984862</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>0.5309036418355016</t>
+          <t>0.3099682900793622</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>0.40202434534917986</t>
+          <t>0.20993903421924998</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>0.28665606943615307</t>
+          <t>0.33902040328257105</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.9456603046006401</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>0.44095647355654227</t>
+          <t>0.20621573915694913</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.9456603046006401</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>0.578088439754593</t>
+          <t>0.31408921073763896</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>0.36337089045331267</t>
+          <t>0.18828970516708243</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.9456603046006401</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>0.4418536735667695</t>
+          <t>0.29232311147744583</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>0.2507915352042477</t>
+          <t>0.3034991801222441</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.9456603046006401</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>0.4510034246105668</t>
+          <t>0.29666344210812806</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>0.2578035345308587</t>
+          <t>0.16247513098660032</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>0.25780353453085914</t>
+          <t>0.16247513098660024</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3554,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>0.27127824161302255</t>
+          <t>0.15625692022998575</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>0.24548668393693546</t>
+          <t>0.16247513098660024</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>0.3436442285029989</t>
+          <t>0.16295783411234008</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>0.27127824161302255</t>
+          <t>0.15625692022998575</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>0.24548668393693546</t>
+          <t>0.16247513098660024</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>0.34364422850299886</t>
+          <t>0.17362101880171377</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>0.2533756357519133</t>
+          <t>0.1696402157360247</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>0.24548668393693546</t>
+          <t>0.16247513098660024</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>0.2845206727574669</t>
+          <t>0.1696402157360247</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>0.3473887699575347</t>
+          <t>0.28085248183649003</t>
         </is>
       </c>
     </row>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>0.3477783984578286</t>
+          <t>0.2904336506587351</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>0.42770828137352684</t>
+          <t>0.31599575119442</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>0.3494303868617336</t>
+          <t>0.1457999419469777</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>0.2687499179593845</t>
+          <t>0.1780908002492842</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>0.4471742512810562</t>
+          <t>0.2918968298033054</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>0.29114716854259876</t>
+          <t>0.2461439181073907</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>0.2981611106030612</t>
+          <t>0.26438490806685266</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>0.3765001858869249</t>
+          <t>0.3281416048044844</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>0.31571105829482743</t>
+          <t>0.3619467860520615</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>0.31403152086999003</t>
+          <t>0.37346814573636616</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>0.36370050938568116</t>
+          <t>0.32936478636302646</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>0.18646802038688798</t>
+          <t>0.17592018707135432</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>0.42603399094958966</t>
+          <t>0.2527570562917229</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>0.20894377738414507</t>
+          <t>0.16247513098660024</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>0.4416525341971574</t>
+          <t>0.2683755102288626</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>0.9468188316776022</t>
+          <t>0.962412735462992</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>0.26083318805225364</t>
+          <t>0.16247513098660024</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>0.22564652359495185</t>
+          <t>0.23514000819026454</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>0.4489486003019205</t>
+          <t>0.25110777828990904</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.9456603046006401</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>0.5634975534769824</t>
+          <t>0.35021562594049876</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>0.4158015886752176</t>
+          <t>0.2487663308241551</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.9456603046006401</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>0.536498804817364</t>
+          <t>0.301085401444314</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>0.21995458943518553</t>
+          <t>0.2877546936208724</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.9456603046006401</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>0.5209326478490961</t>
+          <t>0.29881539812234653</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>0.21258293825892755</t>
+          <t>0.1265939413251215</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>0.21258293825892763</t>
+          <t>0.12659394132512167</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>0.21933784789392138</t>
+          <t>0.1473593871812285</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>0.18204272258992132</t>
+          <t>0.10966056895684723</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>0.2984236322310678</t>
+          <t>0.15347664720931947</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>0.21933784789392138</t>
+          <t>0.1473593871812285</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>0.18204272258992132</t>
+          <t>0.10966056895684723</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>0.2984236322310679</t>
+          <t>0.15686858793936181</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>0.19398455795401462</t>
+          <t>0.12231599280141188</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>0.18204272258992132</t>
+          <t>0.10966056895684723</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>0.23930007648553578</t>
+          <t>0.1439495037042423</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>0.4587908933794657</t>
+          <t>0.3044281762199869</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>0.368787446018571</t>
+          <t>0.2954435672571777</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>0.5370168516652402</t>
+          <t>0.33884312421233814</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>0.322388314839432</t>
+          <t>0.15169482185234584</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>0.31947123520887455</t>
+          <t>0.17809552549077762</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>0.4397260287056144</t>
+          <t>0.3113632181098921</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>0.3455295020416162</t>
+          <t>0.33926573397541687</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>0.3869739640227722</t>
+          <t>0.30548480727627014</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>0.40073246032336807</t>
+          <t>0.3547107756418595</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>0.36471760013886634</t>
+          <t>0.40070265225354534</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>0.3678194765940396</t>
+          <t>0.38652192249251877</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>0.4243254884942007</t>
+          <t>0.3575385705906562</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>0.18531923311697687</t>
+          <t>0.18700471942945293</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>0.3774131780308531</t>
+          <t>0.259917222901376</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>0.15357320137094524</t>
+          <t>0.12659394132512167</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>0.4498220860494694</t>
+          <t>0.23774957733404423</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.9456603046006401</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>0.21258293825892768</t>
+          <t>0.12659394132512167</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>0.22088528756633286</t>
+          <t>0.24346491932246364</t>
         </is>
       </c>
     </row>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>0.4489486003019205</t>
+          <t>0.19475097719150625</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.9940302114769562</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.998509098917632</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>0.4489486003019205</t>
+          <t>0.19475097719150625</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.8807928977764421</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>0.9983636725938129</t>
+          <t>0.5883226813679943</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>0.4489486003019205</t>
+          <t>0.19475097719150625</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>0.7581959327577178</t>
+          <t>0.5467816674491534</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>0.3882438142267913</t>
+          <t>0.2448960417056968</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>0.38824381422679133</t>
+          <t>0.24489604170569673</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>0.446480697460745</t>
+          <t>0.27024178002611243</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>0.38824381422679133</t>
+          <t>0.24489604170569673</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>0.4884765383476337</t>
+          <t>0.2922560340180931</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>0.446480697460745</t>
+          <t>0.27024178002611277</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>0.3882438142267917</t>
+          <t>0.24489604170569673</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>0.5202225700936652</t>
+          <t>0.3053083359360891</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>0.4643145049035332</t>
+          <t>0.29210406068821154</t>
         </is>
       </c>
     </row>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>0.34632222088317566</t>
+          <t>0.24489604170569673</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>0.4719126785820207</t>
+          <t>0.29210406068821154</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>0.8573392579728359</t>
+          <t>0.5423027800084776</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>0.7926477715661455</t>
+          <t>0.6645739418997428</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.7774837768650052</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>0.8019707319331975</t>
+          <t>0.6455915243432477</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>0.37899534463713713</t>
+          <t>0.27664982398783444</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>0.8299986157969532</t>
+          <t>0.5329617096978312</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>0.9190854481162107</t>
+          <t>0.8137022710385301</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>0.8686331278097014</t>
+          <t>0.5771903906762113</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>0.5046867498057843</t>
+          <t>0.38584125410947834</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>0.8760044523606563</t>
+          <t>0.4563906923193421</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>0.9253745019461711</t>
+          <t>0.5943459358228518</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>0.9379113496604994</t>
+          <t>0.5943459358228518</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>0.37413280322597214</t>
+          <t>0.34003629050274276</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>0.39857205129193873</t>
+          <t>0.3441002916569224</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>0.3353966885149807</t>
+          <t>0.1893738335189246</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>0.4244299448194171</t>
+          <t>0.3952378081110826</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>0.3615662408219133</t>
+          <t>0.1771792426131717</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>0.3564977824807596</t>
+          <t>0.24489604170569673</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>0.2693682556481319</t>
+          <t>0.2755346072063801</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>0.5634975534769824</t>
+          <t>0.35021562594049876</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>0.4517486125877636</t>
+          <t>0.22273798928491303</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.9456603046006401</t>
         </is>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>0.536498804817364</t>
+          <t>0.339657011872978</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>0.2543164471555113</t>
+          <t>0.3154347489619994</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.9456603046006401</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>0.5209326478490961</t>
+          <t>0.3209250880571396</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>0.21258293825892755</t>
+          <t>0.1265939413251215</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>0.21258293825892763</t>
+          <t>0.12659394132512167</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>0.20735550658973934</t>
+          <t>0.1498459925215455</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>0.17006038128573947</t>
+          <t>0.09250403481676837</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>0.2984236322310678</t>
+          <t>0.15961395534309106</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>0.20735550658973934</t>
+          <t>0.1498459925215455</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>0.17006038128573947</t>
+          <t>0.09250403481676837</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>0.2984236322310679</t>
+          <t>0.15961395534309106</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>0.18200221664983282</t>
+          <t>0.1309859872870772</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>0.17006038128573947</t>
+          <t>0.09250403481676837</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>0.23930007648553578</t>
+          <t>0.1439495037042423</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>0.4587908933794657</t>
+          <t>0.3044281762199869</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>0.46125632916264636</t>
+          <t>0.2954435672571777</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>0.5370168516652402</t>
+          <t>0.33884312421233814</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>0.34985916928134986</t>
+          <t>0.2615415725080616</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>0.31947123520887455</t>
+          <t>0.17809552549077762</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5730,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>0.4397260287056144</t>
+          <t>0.3248275837128229</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>0.34985916928134997</t>
+          <t>0.33926573397541687</t>
         </is>
       </c>
     </row>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>0.3869739640227722</t>
+          <t>0.30548480727627014</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>0.40073246032336807</t>
+          <t>0.3547107756418595</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>0.394185559407791</t>
+          <t>0.40070265225354534</t>
         </is>
       </c>
     </row>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>0.3835043629039083</t>
+          <t>0.38652192249251877</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>0.4243254884942007</t>
+          <t>0.3575385705906562</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>0.2177364844952045</t>
+          <t>0.18700471942945293</t>
         </is>
       </c>
     </row>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>0.3774131780308531</t>
+          <t>0.26546785335139306</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>0.15357320137094524</t>
+          <t>0.12659394132512167</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>0.4498220860494694</t>
+          <t>0.2436630447260304</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.9456603046006401</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>0.21258293825892768</t>
+          <t>0.12659394132512167</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>0.22088528756633286</t>
+          <t>0.32604909909935553</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.8996792001540689</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>0.5634975534769824</t>
+          <t>0.35021562594049876</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.962412735462992</t>
         </is>
       </c>
     </row>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>0.6395556341875601</t>
+          <t>0.5077175623821601</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>0.5634975534769824</t>
+          <t>0.35021562594049876</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>0.7434751465197066</t>
+          <t>0.5479754620583437</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>0.38924031658522934</t>
+          <t>0.3379380763696062</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>0.38924031658522934</t>
+          <t>0.3379380763696062</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>0.4778540706077184</t>
+          <t>0.31495990551541436</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>0.3817202298523469</t>
+          <t>0.3379380763696062</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>0.5267377327528151</t>
+          <t>0.36320183331660955</t>
         </is>
       </c>
     </row>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>0.4778540706077184</t>
+          <t>0.31813985261838695</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>0.3817202298523469</t>
+          <t>0.3379380763696062</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>0.5267377327528151</t>
+          <t>0.3632018333166094</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>0.5080428779537469</t>
+          <t>0.3898462338866773</t>
         </is>
       </c>
     </row>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>0.3817202298523469</t>
+          <t>0.3379380763696062</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>0.5080428779537469</t>
+          <t>0.3898462338866773</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6257,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>0.8058791336588795</t>
+          <t>0.5287912554478216</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>0.6832762852297066</t>
+          <t>0.6439514143821659</t>
         </is>
       </c>
     </row>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.8359254329801444</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>0.8452890803966985</t>
+          <t>0.7903692169506279</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>0.33424246523113416</t>
+          <t>0.20008651448705891</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>0.8720092226615503</t>
+          <t>0.498016292316778</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.7903692169506279</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>0.9156850719552424</t>
+          <t>0.5894529562465985</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>0.5400528360323891</t>
+          <t>0.3696150124861425</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>0.8608517786720337</t>
+          <t>0.4806759926318346</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.6342366343809743</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.6342366343809743</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>0.5756676449959574</t>
+          <t>0.38597398177222636</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>0.5886371641821949</t>
+          <t>0.36112012645706904</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>0.43364136066036635</t>
+          <t>0.20788923839145598</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>0.5808558150445273</t>
+          <t>0.420463357611206</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>0.578088439754593</t>
+          <t>0.31408921073763896</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>0.3817202298523469</t>
+          <t>0.3379380763696062</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>0.26755546412460474</t>
+          <t>0.22362644968930956</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>0.4517486125877633</t>
+          <t>0.22273798928491303</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.8698195649472922</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>0.8625701569942859</t>
+          <t>0.43500938256601335</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>0.3850428566631164</t>
+          <t>0.23771138206148612</t>
         </is>
       </c>
     </row>
@@ -6648,7 +6648,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>0.635051819783</t>
+          <t>0.44735030863519615</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>0.3882438142267913</t>
+          <t>0.21131081119842593</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>0.38824381422679144</t>
+          <t>0.211310811198426</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>0.446480697460745</t>
+          <t>0.27472066746678814</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>0.38824381422679133</t>
+          <t>0.211310811198426</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>0.4884765383476337</t>
+          <t>0.3097872233767651</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>0.446480697460745</t>
+          <t>0.27472066746678847</t>
         </is>
       </c>
     </row>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>0.3882438142267917</t>
+          <t>0.211310811198426</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>0.5202225700936652</t>
+          <t>0.3097872233767652</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>0.44034207189734015</t>
+          <t>0.2607038581197084</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>0.32850241585959344</t>
+          <t>0.211310811198426</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>0.4719126785820207</t>
+          <t>0.2607038581197084</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>0.8573392579728359</t>
+          <t>0.5883226813679943</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>0.7926477715661455</t>
+          <t>0.7572598687903215</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.8666885539038427</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>0.8019707319331975</t>
+          <t>0.5475021598609094</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>0.37899534463713713</t>
+          <t>0.3109655223563041</t>
         </is>
       </c>
     </row>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>0.8299986157969532</t>
+          <t>0.6111931539075189</t>
         </is>
       </c>
     </row>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>0.9190854481162107</t>
+          <t>0.777419572955834</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>0.8686331278097014</t>
+          <t>0.5816692781168872</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>0.5046867498057843</t>
+          <t>0.3950914114560876</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>0.8760044523606563</t>
+          <t>0.530379085151868</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>0.9253745019461711</t>
+          <t>0.7468319054090374</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>0.9379113496604994</t>
+          <t>0.7468319054090374</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>0.3826521727059141</t>
+          <t>0.3445151779434186</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>0.3705676712040307</t>
+          <t>0.3463699614321468</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>0.32450509286699825</t>
+          <t>0.17944273564211338</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>0.4244299448194171</t>
+          <t>0.32781936731421807</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>0.30217031313062775</t>
+          <t>0.18828970516708243</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>0.3564977824807596</t>
+          <t>0.211310811198426</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>0.2372895844395379</t>
+          <t>0.2751447742347602</t>
         </is>
       </c>
     </row>
@@ -7175,7 +7175,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>0.536498804817364</t>
+          <t>0.301085401444314</t>
         </is>
       </c>
     </row>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>0.2522235459541428</t>
+          <t>0.3209250880571396</t>
         </is>
       </c>
     </row>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.9456603046006401</t>
         </is>
       </c>
     </row>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>0.5209326478490961</t>
+          <t>0.3089895192173841</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>0.21258293825892755</t>
+          <t>0.1265939413251215</t>
         </is>
       </c>
     </row>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>0.21258293825892763</t>
+          <t>0.12659394132512167</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>0.20735550658973934</t>
+          <t>0.1394108679653121</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>0.1700603812857393</t>
+          <t>0.09250403481676853</t>
         </is>
       </c>
     </row>
@@ -7311,7 +7311,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>0.2984236322310678</t>
+          <t>0.14858097796349473</t>
         </is>
       </c>
     </row>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>0.20735550658973934</t>
+          <t>0.13941086796531194</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>0.1700603812857393</t>
+          <t>0.09250403481676853</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>0.2984236322310679</t>
+          <t>0.15686858793936181</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>0.1820022166498326</t>
+          <t>0.12002526953836258</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>0.1700603812857393</t>
+          <t>0.09250403481676853</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7413,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>0.23930007648553578</t>
+          <t>0.1439495037042423</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>0.4587908933794657</t>
+          <t>0.3044281762199869</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>0.4097466069747651</t>
+          <t>0.2954435672571777</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>0.5370168516652402</t>
+          <t>0.33884312421233814</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>0.3498591692813497</t>
+          <t>0.22083065937383436</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>0.31947123520887455</t>
+          <t>0.17809552549077762</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7515,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>0.4397260287056144</t>
+          <t>0.3113632181098921</t>
         </is>
       </c>
     </row>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>0.3498591692813498</t>
+          <t>0.33926573397541687</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>0.403766935789724</t>
+          <t>0.30548480727627014</t>
         </is>
       </c>
     </row>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>0.40073246032336807</t>
+          <t>0.3547107756418595</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>0.4379139324580045</t>
+          <t>0.40070265225354534</t>
         </is>
       </c>
     </row>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>0.4016946174619939</t>
+          <t>0.38652192249251877</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>0.4243254884942007</t>
+          <t>0.3575385705906562</t>
         </is>
       </c>
     </row>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>0.2541833949159426</t>
+          <t>0.18700471942945293</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>0.3774131780308531</t>
+          <t>0.23469726149658898</t>
         </is>
       </c>
     </row>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>0.15357320137094524</t>
+          <t>0.12659394132512167</t>
         </is>
       </c>
     </row>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>0.4498220860494694</t>
+          <t>0.24782261990313018</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.9456603046006401</t>
         </is>
       </c>
     </row>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>0.21258293825892768</t>
+          <t>0.12659394132512167</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>0.22088528756633286</t>
+          <t>0.32604909909935553</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>0.6994286463470526</t>
+          <t>0.42200932507208694</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>0.536498804817364</t>
+          <t>0.301085401444314</t>
         </is>
       </c>
     </row>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>0.8516026974880263</t>
+          <t>0.3995983610165667</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>0.3806089982851191</t>
+          <t>0.3594030053946978</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>0.3806089982851191</t>
+          <t>0.3594030053946978</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>0.47248578090554894</t>
+          <t>0.2986397245418835</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>0.36957531929400844</t>
+          <t>0.3594030053946978</t>
         </is>
       </c>
     </row>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>0.5191624752214343</t>
+          <t>0.3550500807967017</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>0.47248578090554927</t>
+          <t>0.31813985261838695</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>0.4079598438416354</t>
+          <t>0.3594030053946978</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>0.5152078252272999</t>
+          <t>0.35505008079670153</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>0.4741127058249118</t>
+          <t>0.41680150200690924</t>
         </is>
       </c>
     </row>
@@ -7957,7 +7957,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>0.36591862272593223</t>
+          <t>0.3594030053946978</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>0.49863350108749305</t>
+          <t>0.41680150200690924</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>0.8540566215360029</t>
+          <t>0.49629988125218044</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>0.7984339299248802</t>
+          <t>0.8934100923660718</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.8818806233415392</t>
         </is>
       </c>
     </row>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>0.8162024295877968</t>
+          <t>0.7981020598379996</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>0.405357165964314</t>
+          <t>0.2787423296929634</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8076,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>0.9209959897596507</t>
+          <t>0.7097010086190364</t>
         </is>
       </c>
     </row>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.9999999999999996</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8110,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>0.9173221743734815</t>
+          <t>0.6395968439542234</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>0.5364623390185153</t>
+          <t>0.5546788153964514</t>
         </is>
       </c>
     </row>
@@ -8144,7 +8144,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>0.9307941906810291</t>
+          <t>0.5900758307618341</t>
         </is>
       </c>
     </row>
@@ -8161,7 +8161,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.7802515065392427</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.7802515065392427</t>
         </is>
       </c>
     </row>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>0.45194981450204613</t>
+          <t>0.3688852039152788</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>0.4376903873635428</t>
+          <t>0.3853614108258934</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>0.3769409211823908</t>
+          <t>0.22465402888199132</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>0.42731417492424423</t>
+          <t>0.3181818181818176</t>
         </is>
       </c>
     </row>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>0.4418536735667695</t>
+          <t>0.29232311147744583</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>0.36591862272593223</t>
+          <t>0.3594030053946978</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>0.288593057773524</t>
+          <t>0.20413248433417683</t>
         </is>
       </c>
     </row>
@@ -8314,7 +8314,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>0.14738197038804532</t>
+          <t>0.20826137316383647</t>
         </is>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>0.8477784614627688</t>
+          <t>0.8780456892512382</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>0.268204942435083</t>
+          <t>0.16159218234335646</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>0.2682049424350829</t>
+          <t>0.16159218234335646</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>0.059373915292476244</t>
+          <t>0.13468477031416778</t>
         </is>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>0.053945467249996305</t>
+          <t>0.08899140014435837</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>0.3441750308362601</t>
+          <t>0.19836587671858955</t>
         </is>
       </c>
     </row>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>0.05937391529247657</t>
+          <t>0.1346847703141681</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>0.053945467249996305</t>
+          <t>0.08899140014435837</t>
         </is>
       </c>
     </row>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>0.30482753369762094</t>
+          <t>0.18722439954420184</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>0.047370830724187636</t>
+          <t>0.11237838457515846</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>0.0433289244145246</t>
+          <t>0.08899140014435837</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>0.30099223842911754</t>
+          <t>0.1876286863227228</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>0.7271546832734901</t>
+          <t>0.5154738194531265</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>0.40001904828831286</t>
+          <t>0.5186553577121903</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>0.7375350455219145</t>
+          <t>0.27617570349051024</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>0.30679453442122123</t>
+          <t>0.28750426902798937</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>0.5264096875566026</t>
+          <t>0.2935553994023938</t>
         </is>
       </c>
     </row>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>0.3162085370861655</t>
+          <t>0.22616203514687297</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>0.4535101740761573</t>
+          <t>0.41772896408739674</t>
         </is>
       </c>
     </row>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>0.4292958487504502</t>
+          <t>0.2882353244676383</t>
         </is>
       </c>
     </row>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>0.3910766875264714</t>
+          <t>0.24222306082822287</t>
         </is>
       </c>
     </row>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>0.3906819264562249</t>
+          <t>0.3636632215926315</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>0.36180263374807176</t>
+          <t>0.2968681391416453</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>0.5069607424188433</t>
+          <t>0.36448949556192894</t>
         </is>
       </c>
     </row>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>0.2925982223725074</t>
+          <t>0.3996792001540687</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>0.6181881588970374</t>
+          <t>0.46480839887402153</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>0.1627155831712404</t>
+          <t>0.15804315012487277</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>0.5673984718395855</t>
+          <t>0.5255545545886611</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>0.2507915352042477</t>
+          <t>0.23472827611706595</t>
         </is>
       </c>
     </row>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>0.18906438649048338</t>
+          <t>0.16159218234335646</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>0.30471933043796173</t>
+          <t>0.23351466907773075</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>0.5209326478490961</t>
+          <t>0.29881539812234653</t>
         </is>
       </c>
     </row>
@@ -8875,7 +8875,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>0.21258293825892755</t>
+          <t>0.1265939413251215</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>0.21258293825892763</t>
+          <t>0.12659394132512167</t>
         </is>
       </c>
     </row>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>0.1685878070530921</t>
+          <t>0.11737822302039569</t>
         </is>
       </c>
     </row>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>0.13129268174909223</t>
+          <t>0.04852520677746516</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>0.2984236322310678</t>
+          <t>0.14551708240159764</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>0.1685878070530921</t>
+          <t>0.15649106290570144</t>
         </is>
       </c>
     </row>
@@ -8977,7 +8977,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>0.13129268174909223</t>
+          <t>0.04852520677746516</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>0.2984236322310679</t>
+          <t>0.15686858793936181</t>
         </is>
       </c>
     </row>
@@ -9011,7 +9011,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>0.1432345171131857</t>
+          <t>0.15649106290570144</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>0.13129268174909223</t>
+          <t>0.04852520677746516</t>
         </is>
       </c>
     </row>
@@ -9045,7 +9045,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>0.23930007648553578</t>
+          <t>0.15649106290570144</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>0.4587908933794657</t>
+          <t>0.3044281762199869</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9079,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>0.368787446018571</t>
+          <t>0.31173088879573363</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>0.5370168516652402</t>
+          <t>0.33884312421233814</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>0.322388314839432</t>
+          <t>0.1282761905782027</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>0.31947123520887455</t>
+          <t>0.17809552549077762</t>
         </is>
       </c>
     </row>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>0.4397260287056144</t>
+          <t>0.3113632181098921</t>
         </is>
       </c>
     </row>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>0.3455295020416162</t>
+          <t>0.33926573397541687</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>0.3869739640227722</t>
+          <t>0.30548480727627014</t>
         </is>
       </c>
     </row>
@@ -9198,7 +9198,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>0.40073246032336807</t>
+          <t>0.3547107756418595</t>
         </is>
       </c>
     </row>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>0.36471760013886634</t>
+          <t>0.40070265225354534</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>0.3678194765940396</t>
+          <t>0.38652192249251877</t>
         </is>
       </c>
     </row>
@@ -9249,7 +9249,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>0.4243254884942007</t>
+          <t>0.3575385705906562</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>0.18531923311697687</t>
+          <t>0.18700471942945293</t>
         </is>
       </c>
     </row>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>0.3774131780308531</t>
+          <t>0.22940248780543196</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>0.15357320137094524</t>
+          <t>0.12659394132512167</t>
         </is>
       </c>
     </row>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>0.4498220860494694</t>
+          <t>0.23774957733404423</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.9456603046006401</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>0.21258293825892768</t>
+          <t>0.12659394132512167</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>0.22088528756633286</t>
+          <t>0.24346491932246364</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9385,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>0.2738288929129448</t>
+          <t>0.1747318249424422</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>0.2738288929129448</t>
+          <t>0.1747318249424422</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>0.16320088132864635</t>
+          <t>0.2684623318439061</t>
         </is>
       </c>
     </row>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>0.1362630317338009</t>
+          <t>0.1747318249424422</t>
         </is>
       </c>
     </row>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>0.3652260070455467</t>
+          <t>0.2949843129908722</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>0.16320088132864635</t>
+          <t>0.2684623318439061</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>0.1362630317338009</t>
+          <t>0.1747318249424422</t>
         </is>
       </c>
     </row>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>0.329152525116918</t>
+          <t>0.2949843129908719</t>
         </is>
       </c>
     </row>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>0.14374711268156024</t>
+          <t>0.21008506227912357</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>0.1362630317338009</t>
+          <t>0.1747318249424422</t>
         </is>
       </c>
     </row>
@@ -9555,7 +9555,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>0.31080294981359924</t>
+          <t>0.21008506227912357</t>
         </is>
       </c>
     </row>
@@ -9572,7 +9572,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>0.6817541071682018</t>
+          <t>0.6041132405869931</t>
         </is>
       </c>
     </row>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>0.5301165441561463</t>
+          <t>0.7117835985824991</t>
         </is>
       </c>
     </row>
@@ -9606,7 +9606,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>0.7218853103837246</t>
+          <t>0.31705000559293534</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>0.3012885917506143</t>
+          <t>0.2503344503143592</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>0.5412772448460308</t>
+          <t>0.40014530703632134</t>
         </is>
       </c>
     </row>
@@ -9657,7 +9657,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>0.37626595675237545</t>
+          <t>0.32379964140239514</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>0.4313493973075634</t>
+          <t>0.41772896408739674</t>
         </is>
       </c>
     </row>
@@ -9691,7 +9691,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>0.42035678112696123</t>
+          <t>0.3723983029713889</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>0.4249702586703673</t>
+          <t>0.284362611749012</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>0.440914371455386</t>
+          <t>0.44737240076336177</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>0.3832730583865667</t>
+          <t>0.3621454625539954</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>0.4746910443717528</t>
+          <t>0.36448949556192883</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>0.53590948770304</t>
+          <t>0.5717932789432961</t>
         </is>
       </c>
     </row>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>0.6368374064429086</t>
+          <t>0.5909036008135204</t>
         </is>
       </c>
     </row>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>0.1587729291109816</t>
+          <t>0.15804315012487277</t>
         </is>
       </c>
     </row>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>0.7167311644121463</t>
+          <t>0.7064982900676187</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>0.4456250292065934</t>
+          <t>0.2608664600840174</t>
         </is>
       </c>
     </row>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>0.1923161856139166</t>
+          <t>0.1747318249424422</t>
         </is>
       </c>
     </row>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>0.3362828341322844</t>
+          <t>0.23351466907773075</t>
         </is>
       </c>
     </row>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>0.5946479588255665</t>
+          <t>0.3576637518003118</t>
         </is>
       </c>
     </row>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.5695191985273463</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>0.5883237659348974</t>
+          <t>0.42713058429965534</t>
         </is>
       </c>
     </row>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>0.5946479588255666</t>
+          <t>0.42892777802092075</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -10048,7 +10048,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>0.699092273711303</t>
+          <t>0.48324007379100997</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>0.5998892071521699</t>
+          <t>0.40186782619476363</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>0.44784557471932773</t>
+          <t>0.538000517892964</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>0.49177207588498895</t>
+          <t>0.41145968847318215</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>0.5131668748329558</t>
+          <t>0.42941017497324335</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>0.4353828192990374</t>
+          <t>0.2165673556346486</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>0.44578885501758625</t>
+          <t>0.4114596884731822</t>
         </is>
       </c>
     </row>
@@ -10167,7 +10167,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>0.5060883604535684</t>
+          <t>0.36903047532984845</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>0.47026710937760235</t>
+          <t>0.3594030053946979</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>0.49191655770842246</t>
+          <t>0.4189504628541155</t>
         </is>
       </c>
     </row>
@@ -10218,7 +10218,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>0.5133633663215261</t>
+          <t>0.4114596884731822</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>0.5487540105642498</t>
+          <t>0.4442970393380977</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>0.5010673191136287</t>
+          <t>0.3836227252527314</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10269,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>0.6225509733003602</t>
+          <t>0.33564058183128165</t>
         </is>
       </c>
     </row>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>0.36251223440722047</t>
+          <t>0.16159218234335646</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>0.7082119425999194</t>
+          <t>0.529181152383134</t>
         </is>
       </c>
     </row>
@@ -10320,7 +10320,7 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>0.5997663863335141</t>
+          <t>0.4410652728576531</t>
         </is>
       </c>
     </row>
@@ -10337,7 +10337,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>0.2578035345308587</t>
+          <t>0.14334637218747343</t>
         </is>
       </c>
     </row>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>0.30672140132093767</t>
+          <t>0.2775725935865046</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>0.5883237659348974</t>
+          <t>0.38347323256637567</t>
         </is>
       </c>
     </row>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.5695191985273463</t>
         </is>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>0.5883237659348972</t>
+          <t>0.42713058429965534</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>0.5946479588255666</t>
+          <t>0.42892777802092086</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -10524,7 +10524,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>0.699092273711303</t>
+          <t>0.48324007379100997</t>
         </is>
       </c>
     </row>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>0.5998892071521699</t>
+          <t>0.4018678261947638</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>0.44784557471932773</t>
+          <t>0.538000517892964</t>
         </is>
       </c>
     </row>
@@ -10575,7 +10575,7 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>0.49177207588498895</t>
+          <t>0.41145968847318215</t>
         </is>
       </c>
     </row>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>0.5131668748329558</t>
+          <t>0.42941017497324335</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>0.4353828192990374</t>
+          <t>0.2165673556346486</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>0.44578885501758625</t>
+          <t>0.4114596884731822</t>
         </is>
       </c>
     </row>
@@ -10643,7 +10643,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>0.5060883604535684</t>
+          <t>0.36903047532984845</t>
         </is>
       </c>
     </row>
@@ -10660,7 +10660,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>0.47026710937760235</t>
+          <t>0.3594030053946979</t>
         </is>
       </c>
     </row>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>0.5032583347756449</t>
+          <t>0.4189504628541155</t>
         </is>
       </c>
     </row>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>0.5133633663215261</t>
+          <t>0.4114596884731822</t>
         </is>
       </c>
     </row>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>0.5487540105642498</t>
+          <t>0.4442970393380977</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>0.5010673191136287</t>
+          <t>0.3836227252527314</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>0.6051924982241568</t>
+          <t>0.33564058183128165</t>
         </is>
       </c>
     </row>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>0.36251223440722047</t>
+          <t>0.16939804059955615</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>0.7082119425999194</t>
+          <t>0.529181152383134</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>0.6314267358770039</t>
+          <t>0.44106527285765307</t>
         </is>
       </c>
     </row>
@@ -10813,7 +10813,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>0.25780353453085914</t>
+          <t>0.14334637218747343</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>0.30672140132093767</t>
+          <t>0.2775725935865046</t>
         </is>
       </c>
     </row>
@@ -10864,7 +10864,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>0.5946479588255665</t>
+          <t>0.4289277780209209</t>
         </is>
       </c>
     </row>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>0.93335726001798</t>
+          <t>0.7732266742876339</t>
         </is>
       </c>
     </row>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>0.93335726001798</t>
+          <t>0.7732266742876339</t>
         </is>
       </c>
     </row>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>0.5946479588255668</t>
+          <t>0.4289277780209209</t>
         </is>
       </c>
     </row>
@@ -10932,7 +10932,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>0.8714503627181368</t>
+          <t>0.7732266742876339</t>
         </is>
       </c>
     </row>
@@ -10949,7 +10949,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.7309263775906009</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>0.45085986317538224</t>
+          <t>0.3366994676820696</t>
         </is>
       </c>
     </row>
@@ -10983,7 +10983,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.7309263775906009</t>
         </is>
       </c>
     </row>
@@ -11000,7 +11000,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>0.817734839142674</t>
+          <t>0.6628913794632398</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11017,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>0.525204648105181</t>
+          <t>0.460597557988653</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>0.8095434654182938</t>
+          <t>0.5849671538296208</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>0.5497481184328107</t>
+          <t>0.3847947414168224</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>0.6470145887105037</t>
+          <t>0.46834894291959683</t>
         </is>
       </c>
     </row>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>0.5277330388667048</t>
+          <t>0.3517088070804984</t>
         </is>
       </c>
     </row>
@@ -11102,7 +11102,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>0.7019081561480637</t>
+          <t>0.4601712763145125</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>0.6741306120018394</t>
+          <t>0.6164858344640028</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>0.39345055369706605</t>
+          <t>0.3868685363576826</t>
         </is>
       </c>
     </row>
@@ -11153,7 +11153,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>0.5498978240217546</t>
+          <t>0.6022170653778736</t>
         </is>
       </c>
     </row>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>0.6109114624259868</t>
+          <t>0.4779342086995005</t>
         </is>
       </c>
     </row>
@@ -11187,7 +11187,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>0.6004456355171187</t>
+          <t>0.47821644721158574</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>0.5428479137837368</t>
+          <t>0.3705258382093879</t>
         </is>
       </c>
     </row>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>0.3287451430742155</t>
+          <t>0.14796844168967185</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>0.4931285322331685</t>
+          <t>0.38347323256637567</t>
         </is>
       </c>
     </row>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>0.5621466209068173</t>
+          <t>0.5015054185316191</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>0.27127824161302244</t>
+          <t>0.1498459925215456</t>
         </is>
       </c>
     </row>
@@ -11289,7 +11289,7 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>0.5002783599408707</t>
+          <t>0.38347323256637533</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>0.21119856010004162</t>
+          <t>0.2220423378960735</t>
         </is>
       </c>
     </row>
@@ -11323,7 +11323,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.5695191985273463</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>0.5883237659348972</t>
+          <t>0.42713058429965534</t>
         </is>
       </c>
     </row>
@@ -11357,7 +11357,7 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>0.5946479588255666</t>
+          <t>0.4289277780209209</t>
         </is>
       </c>
     </row>
@@ -11408,7 +11408,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -11425,7 +11425,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>0.699092273711303</t>
+          <t>0.48324007379100997</t>
         </is>
       </c>
     </row>
@@ -11442,7 +11442,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>0.5998892071521699</t>
+          <t>0.4018678261947638</t>
         </is>
       </c>
     </row>
@@ -11459,7 +11459,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>0.44784557471932773</t>
+          <t>0.538000517892964</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>0.49177207588498895</t>
+          <t>0.41145968847318215</t>
         </is>
       </c>
     </row>
@@ -11493,7 +11493,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>0.5131668748329558</t>
+          <t>0.42941017497324335</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>0.4353828192990374</t>
+          <t>0.2165673556346486</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>0.44578885501758625</t>
+          <t>0.4114596884731822</t>
         </is>
       </c>
     </row>
@@ -11544,7 +11544,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>0.5060883604535684</t>
+          <t>0.36903047532984845</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>0.47026710937760235</t>
+          <t>0.3594030053946979</t>
         </is>
       </c>
     </row>
@@ -11578,7 +11578,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>0.49191655770842246</t>
+          <t>0.4189504628541155</t>
         </is>
       </c>
     </row>
@@ -11595,7 +11595,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>0.5133633663215261</t>
+          <t>0.4114596884731822</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>0.5487540105642498</t>
+          <t>0.4442970393380977</t>
         </is>
       </c>
     </row>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>0.5010673191136287</t>
+          <t>0.3836227252527314</t>
         </is>
       </c>
     </row>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>0.6225509733003604</t>
+          <t>0.33564058183128165</t>
         </is>
       </c>
     </row>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>0.36251223440722047</t>
+          <t>0.15650359731530505</t>
         </is>
       </c>
     </row>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>0.6629562793532694</t>
+          <t>0.5746356978376793</t>
         </is>
       </c>
     </row>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>0.5997663863335141</t>
+          <t>0.44106527285765307</t>
         </is>
       </c>
     </row>
@@ -11714,7 +11714,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>0.24548668393693537</t>
+          <t>0.1341771196721336</t>
         </is>
       </c>
     </row>
@@ -11731,7 +11731,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>0.24441217683631616</t>
+          <t>0.2775725935865046</t>
         </is>
       </c>
     </row>
@@ -11765,7 +11765,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>0.93335726001798</t>
+          <t>0.7732266742876339</t>
         </is>
       </c>
     </row>
@@ -11782,7 +11782,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.5695191985273463</t>
         </is>
       </c>
     </row>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>0.9690632527820694</t>
+          <t>0.8112781244591326</t>
         </is>
       </c>
     </row>
@@ -11816,7 +11816,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.6840384356390417</t>
         </is>
       </c>
     </row>
@@ -11833,7 +11833,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.5695191985273463</t>
         </is>
       </c>
     </row>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.6840384356390417</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>0.7273495737935876</t>
+          <t>0.7292408409492052</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>0.5063660993266962</t>
+          <t>0.47103651370034344</t>
         </is>
       </c>
     </row>
@@ -11901,7 +11901,7 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>0.6988187944586057</t>
+          <t>0.5926763005597211</t>
         </is>
       </c>
     </row>
@@ -11918,7 +11918,7 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>0.5071708359846883</t>
+          <t>0.34400328801932584</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>0.5881108718296884</t>
+          <t>0.4452795548762268</t>
         </is>
       </c>
     </row>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>0.4444922922391948</t>
+          <t>0.3118711727932671</t>
         </is>
       </c>
     </row>
@@ -11969,7 +11969,7 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>0.5807538371305797</t>
+          <t>0.422752410475792</t>
         </is>
       </c>
     </row>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>0.6326841628929499</t>
+          <t>0.5366488526424774</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>0.4190270929504037</t>
+          <t>0.3610065267740943</t>
         </is>
       </c>
     </row>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>0.5483908655491858</t>
+          <t>0.5155669632481046</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>0.5366316648266878</t>
+          <t>0.4237741878014455</t>
         </is>
       </c>
     </row>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>0.5511550820931268</t>
+          <t>0.4854460399011119</t>
         </is>
       </c>
     </row>
@@ -12071,7 +12071,7 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>0.5055108718194654</t>
+          <t>0.3687627838450599</t>
         </is>
       </c>
     </row>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>0.3359425625629221</t>
+          <t>0.24900597079096856</t>
         </is>
       </c>
     </row>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>0.7116109233184235</t>
+          <t>0.3932954903110028</t>
         </is>
       </c>
     </row>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>0.552019366093709</t>
+          <t>0.4906584921568521</t>
         </is>
       </c>
     </row>
@@ -12139,7 +12139,7 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>0.3436442285029989</t>
+          <t>0.15961395534309114</t>
         </is>
       </c>
     </row>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.5695191985273463</t>
         </is>
       </c>
     </row>
@@ -12173,7 +12173,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>0.3652618778289934</t>
+          <t>0.2212576703070361</t>
         </is>
       </c>
     </row>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>0.5320243916869024</t>
+          <t>0.3576637518003118</t>
         </is>
       </c>
     </row>
@@ -12207,7 +12207,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>0.8714503627181368</t>
+          <t>0.7732266742876339</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.6840384356390417</t>
         </is>
       </c>
     </row>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>0.4082692084278821</t>
+          <t>0.3366994676820697</t>
         </is>
       </c>
     </row>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.6840384356390417</t>
         </is>
       </c>
     </row>
@@ -12275,7 +12275,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>0.817734839142674</t>
+          <t>0.6628913794632398</t>
         </is>
       </c>
     </row>
@@ -12292,7 +12292,7 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>0.525204648105181</t>
+          <t>0.460597557988653</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>0.8095434654182938</t>
+          <t>0.5849671538296208</t>
         </is>
       </c>
     </row>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>0.5497481184328107</t>
+          <t>0.3847947414168223</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>0.6470145887105037</t>
+          <t>0.46834894291959683</t>
         </is>
       </c>
     </row>
@@ -12360,7 +12360,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>0.5277330388667048</t>
+          <t>0.3517088070804984</t>
         </is>
       </c>
     </row>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>0.7019081561480637</t>
+          <t>0.46017127631451243</t>
         </is>
       </c>
     </row>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>0.6741306120018397</t>
+          <t>0.6164858344640031</t>
         </is>
       </c>
     </row>
@@ -12411,7 +12411,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>0.39345055369706605</t>
+          <t>0.3868685363576826</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>0.5498978240217546</t>
+          <t>0.6022170653778736</t>
         </is>
       </c>
     </row>
@@ -12445,7 +12445,7 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>0.6109114624259868</t>
+          <t>0.4779342086995005</t>
         </is>
       </c>
     </row>
@@ -12462,7 +12462,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>0.6004456355171187</t>
+          <t>0.47821644721158574</t>
         </is>
       </c>
     </row>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>0.5428479137837365</t>
+          <t>0.37052583820938806</t>
         </is>
       </c>
     </row>
@@ -12496,7 +12496,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>0.3287451430742155</t>
+          <t>0.14796844168967185</t>
         </is>
       </c>
     </row>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>0.484429617863956</t>
+          <t>0.42713058429965534</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>0.5621466209068173</t>
+          <t>0.5015054185316191</t>
         </is>
       </c>
     </row>
@@ -12547,7 +12547,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>0.27127824161302244</t>
+          <t>0.1498459925215456</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>0.5002783599408707</t>
+          <t>0.35766375180031185</t>
         </is>
       </c>
     </row>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>0.21119856010004162</t>
+          <t>0.2220423378960735</t>
         </is>
       </c>
     </row>
@@ -12598,7 +12598,7 @@
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12615,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>0.5946479588255668</t>
+          <t>0.4289277780209209</t>
         </is>
       </c>
     </row>
@@ -12632,7 +12632,7 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>0.699092273711303</t>
+          <t>0.48324007379100997</t>
         </is>
       </c>
     </row>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>0.5998892071521699</t>
+          <t>0.4018678261947638</t>
         </is>
       </c>
     </row>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>0.44784557471932773</t>
+          <t>0.538000517892964</t>
         </is>
       </c>
     </row>
@@ -12700,7 +12700,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>0.49177207588498895</t>
+          <t>0.41145968847318215</t>
         </is>
       </c>
     </row>
@@ -12717,7 +12717,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>0.5131668748329558</t>
+          <t>0.42941017497324335</t>
         </is>
       </c>
     </row>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>0.4353828192990374</t>
+          <t>0.2165673556346486</t>
         </is>
       </c>
     </row>
@@ -12751,7 +12751,7 @@
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>0.44578885501758625</t>
+          <t>0.4114596884731822</t>
         </is>
       </c>
     </row>
@@ -12768,7 +12768,7 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>0.5060883604535684</t>
+          <t>0.36903047532984845</t>
         </is>
       </c>
     </row>
@@ -12785,7 +12785,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>0.47026710937760235</t>
+          <t>0.3594030053946979</t>
         </is>
       </c>
     </row>
@@ -12802,7 +12802,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>0.49191655770842246</t>
+          <t>0.4189504628541155</t>
         </is>
       </c>
     </row>
@@ -12819,7 +12819,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>0.5133633663215261</t>
+          <t>0.4114596884731822</t>
         </is>
       </c>
     </row>
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>0.5487540105642498</t>
+          <t>0.4442970393380977</t>
         </is>
       </c>
     </row>
@@ -12853,7 +12853,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>0.5010673191136287</t>
+          <t>0.3836227252527314</t>
         </is>
       </c>
     </row>
@@ -12870,7 +12870,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>0.6225509733003604</t>
+          <t>0.33564058183128165</t>
         </is>
       </c>
     </row>
@@ -12887,7 +12887,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>0.36251223440722047</t>
+          <t>0.15650359731530505</t>
         </is>
       </c>
     </row>
@@ -12904,7 +12904,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>0.6261563939499927</t>
+          <t>0.5746356978376793</t>
         </is>
       </c>
     </row>
@@ -12921,7 +12921,7 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>0.5997663863335141</t>
+          <t>0.44106527285765307</t>
         </is>
       </c>
     </row>
@@ -12938,7 +12938,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>0.24548668393693537</t>
+          <t>0.1341771196721336</t>
         </is>
       </c>
     </row>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>0.24441217683631616</t>
+          <t>0.2775725935865046</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>0.8056959500093788</t>
+          <t>0.6214273560444175</t>
         </is>
       </c>
     </row>
@@ -13006,7 +13006,7 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>0.8056959500093788</t>
+          <t>0.6214273560444175</t>
         </is>
       </c>
     </row>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>0.7273495737935876</t>
+          <t>0.7292408409492052</t>
         </is>
       </c>
     </row>
@@ -13057,7 +13057,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>0.5063660993266962</t>
+          <t>0.47103651370034344</t>
         </is>
       </c>
     </row>
@@ -13074,7 +13074,7 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>0.6988187944586057</t>
+          <t>0.5926763005597211</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>0.5071708359846883</t>
+          <t>0.34400328801932584</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>0.6461853495222436</t>
+          <t>0.5746356978376793</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>0.43250995093501293</t>
+          <t>0.36574443015250113</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>0.5807538371305797</t>
+          <t>0.422752410475792</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13159,7 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>0.6326841628929499</t>
+          <t>0.5366488526424774</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>0.4413514374758016</t>
+          <t>0.36574443015250113</t>
         </is>
       </c>
     </row>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>0.5483908655491858</t>
+          <t>0.5155669632481046</t>
         </is>
       </c>
     </row>
@@ -13210,7 +13210,7 @@
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>0.5366316648266879</t>
+          <t>0.4237741878014455</t>
         </is>
       </c>
     </row>
@@ -13227,7 +13227,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>0.5511550820931268</t>
+          <t>0.4854460399011119</t>
         </is>
       </c>
     </row>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>0.5199595912367255</t>
+          <t>0.3687627838450599</t>
         </is>
       </c>
     </row>
@@ -13261,7 +13261,7 @@
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>0.30397745242489976</t>
+          <t>0.2490059707909684</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>0.6157086379221312</t>
+          <t>0.5008831410686673</t>
         </is>
       </c>
     </row>
@@ -13295,7 +13295,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>0.552019366093709</t>
+          <t>0.4906584921568521</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13312,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>0.34364422850299886</t>
+          <t>0.17362101880171393</t>
         </is>
       </c>
     </row>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -13346,7 +13346,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>0.3652618778289933</t>
+          <t>0.2212576703070361</t>
         </is>
       </c>
     </row>
@@ -13363,7 +13363,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>0.45085986317538224</t>
+          <t>0.33573496025298594</t>
         </is>
       </c>
     </row>
@@ -13380,7 +13380,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>0.9015982354056711</t>
+          <t>0.6840384356390417</t>
         </is>
       </c>
     </row>
@@ -13397,7 +13397,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>0.7527107453773279</t>
+          <t>0.4989995845009441</t>
         </is>
       </c>
     </row>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>0.4582840917412809</t>
+          <t>0.4781600259580958</t>
         </is>
       </c>
     </row>
@@ -13431,7 +13431,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>0.8141414893052435</t>
+          <t>0.5133617309952476</t>
         </is>
       </c>
     </row>
@@ -13448,7 +13448,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>0.5547971015649678</t>
+          <t>0.5365333221010176</t>
         </is>
       </c>
     </row>
@@ -13465,7 +13465,7 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>0.5283148995385651</t>
+          <t>0.3426486532845844</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>0.582027607746627</t>
+          <t>0.4455308537837528</t>
         </is>
       </c>
     </row>
@@ -13499,7 +13499,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>0.7089162435418992</t>
+          <t>0.5476747992754054</t>
         </is>
       </c>
     </row>
@@ -13516,7 +13516,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>0.6173049500342045</t>
+          <t>0.5737031408146476</t>
         </is>
       </c>
     </row>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>0.4445534347660251</t>
+          <t>0.4564211070665323</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>0.5705971525482497</t>
+          <t>0.5599167686808405</t>
         </is>
       </c>
     </row>
@@ -13567,7 +13567,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>0.7350215115702312</t>
+          <t>0.4962051968551688</t>
         </is>
       </c>
     </row>
@@ -13584,7 +13584,7 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>0.6821032303925342</t>
+          <t>0.44378459489024097</t>
         </is>
       </c>
     </row>
@@ -13601,7 +13601,7 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>0.5801787489488578</t>
+          <t>0.3294807511035757</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>0.35005428337669114</t>
+          <t>0.15220190883584303</t>
         </is>
       </c>
     </row>
@@ -13635,7 +13635,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>0.5368569052833821</t>
+          <t>0.42892777802092086</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13652,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>0.5833728009265591</t>
+          <t>0.41179657299504585</t>
         </is>
       </c>
     </row>
@@ -13669,7 +13669,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>0.2533756357519133</t>
+          <t>0.14134220442155807</t>
         </is>
       </c>
     </row>
@@ -13686,7 +13686,7 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>0.5629019270795349</t>
+          <t>0.42892777802092086</t>
         </is>
       </c>
     </row>
@@ -13703,7 +13703,7 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>0.24994444892742967</t>
+          <t>0.26669465566455014</t>
         </is>
       </c>
     </row>
@@ -13720,7 +13720,7 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>0.699092273711303</t>
+          <t>0.48324007379100997</t>
         </is>
       </c>
     </row>
@@ -13737,7 +13737,7 @@
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>0.5998892071521699</t>
+          <t>0.4018678261947638</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>0.44784557471932773</t>
+          <t>0.538000517892964</t>
         </is>
       </c>
     </row>
@@ -13771,7 +13771,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>0.49177207588498895</t>
+          <t>0.41145968847318215</t>
         </is>
       </c>
     </row>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>0.5131668748329558</t>
+          <t>0.42941017497324335</t>
         </is>
       </c>
     </row>
@@ -13805,7 +13805,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>0.4353828192990374</t>
+          <t>0.2165673556346486</t>
         </is>
       </c>
     </row>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>0.44578885501758625</t>
+          <t>0.4114596884731822</t>
         </is>
       </c>
     </row>
@@ -13839,7 +13839,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>0.5060883604535684</t>
+          <t>0.36903047532984845</t>
         </is>
       </c>
     </row>
@@ -13856,7 +13856,7 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>0.47026710937760235</t>
+          <t>0.3594030053946979</t>
         </is>
       </c>
     </row>
@@ -13873,7 +13873,7 @@
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>0.49191655770842246</t>
+          <t>0.4189504628541155</t>
         </is>
       </c>
     </row>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>0.5133633663215261</t>
+          <t>0.4114596884731822</t>
         </is>
       </c>
     </row>
@@ -13907,7 +13907,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>0.5487540105642498</t>
+          <t>0.4442970393380977</t>
         </is>
       </c>
     </row>
@@ -13924,7 +13924,7 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>0.5010673191136287</t>
+          <t>0.3836227252527314</t>
         </is>
       </c>
     </row>
@@ -13941,7 +13941,7 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>0.6041184781729552</t>
+          <t>0.33564058183128165</t>
         </is>
       </c>
     </row>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>0.36251223440722047</t>
+          <t>0.15650359731530505</t>
         </is>
       </c>
     </row>
@@ -13975,7 +13975,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>0.5699480893391555</t>
+          <t>0.4813922218413367</t>
         </is>
       </c>
     </row>
@@ -13992,7 +13992,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>0.5997663863335141</t>
+          <t>0.44106527285765307</t>
         </is>
       </c>
     </row>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>0.24548668393693537</t>
+          <t>0.1341771196721336</t>
         </is>
       </c>
     </row>
@@ -14026,7 +14026,7 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>0.8832225588099292</t>
+          <t>0.6321302781219706</t>
         </is>
       </c>
     </row>
@@ -14043,7 +14043,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>0.24441217683631616</t>
+          <t>0.2775725935865046</t>
         </is>
       </c>
     </row>
@@ -14060,7 +14060,7 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>0.7527107453773279</t>
+          <t>0.4989995845009441</t>
         </is>
       </c>
     </row>
@@ -14077,7 +14077,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>0.4582840917412809</t>
+          <t>0.4781600259580958</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>0.8141414893052435</t>
+          <t>0.5133617309952476</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>0.5547971015649678</t>
+          <t>0.5365333221010176</t>
         </is>
       </c>
     </row>
@@ -14128,7 +14128,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>0.5283148995385651</t>
+          <t>0.3426486532845844</t>
         </is>
       </c>
     </row>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>0.582027607746627</t>
+          <t>0.4455308537837528</t>
         </is>
       </c>
     </row>
@@ -14162,7 +14162,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>0.7089162435418992</t>
+          <t>0.5476747992754054</t>
         </is>
       </c>
     </row>
@@ -14179,7 +14179,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>0.6173049500342045</t>
+          <t>0.5737031408146476</t>
         </is>
       </c>
     </row>
@@ -14196,7 +14196,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>0.4445534347660251</t>
+          <t>0.4564211070665323</t>
         </is>
       </c>
     </row>
@@ -14213,7 +14213,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>0.5705971525482497</t>
+          <t>0.5599167686808405</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>0.7350215115702312</t>
+          <t>0.4962051968551688</t>
         </is>
       </c>
     </row>
@@ -14247,7 +14247,7 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>0.6821032303925342</t>
+          <t>0.44378459489024097</t>
         </is>
       </c>
     </row>
@@ -14264,7 +14264,7 @@
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>0.5801787489488578</t>
+          <t>0.3294807511035757</t>
         </is>
       </c>
     </row>
@@ -14281,7 +14281,7 @@
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>0.35005428337669114</t>
+          <t>0.1821498035712831</t>
         </is>
       </c>
     </row>
@@ -14298,7 +14298,7 @@
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>0.7092898346710996</t>
+          <t>0.48324007379100997</t>
         </is>
       </c>
     </row>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>0.5833728009265591</t>
+          <t>0.41179657299504585</t>
         </is>
       </c>
     </row>
@@ -14332,7 +14332,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>0.2845206727574669</t>
+          <t>0.16070193456659423</t>
         </is>
       </c>
     </row>
@@ -14349,7 +14349,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>0.699092273711303</t>
+          <t>0.48324007379100997</t>
         </is>
       </c>
     </row>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>0.3442671400223501</t>
+          <t>0.26669465566455014</t>
         </is>
       </c>
     </row>
@@ -14383,7 +14383,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>0.7035511600721477</t>
+          <t>0.498016292316778</t>
         </is>
       </c>
     </row>
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.8293232953562055</t>
         </is>
       </c>
     </row>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>0.8728341199762156</t>
+          <t>0.7035103037093104</t>
         </is>
       </c>
     </row>
@@ -14434,7 +14434,7 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>0.6148712363209827</t>
+          <t>0.30190842511040644</t>
         </is>
       </c>
     </row>
@@ -14451,7 +14451,7 @@
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>0.7792595439685595</t>
+          <t>0.36888520391527896</t>
         </is>
       </c>
     </row>
@@ -14468,7 +14468,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>0.7881625505131378</t>
+          <t>0.5898135824503619</t>
         </is>
       </c>
     </row>
@@ -14485,7 +14485,7 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>0.772252981554741</t>
+          <t>0.6511840002777499</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>0.48629481408195346</t>
+          <t>0.2808749752206663</t>
         </is>
       </c>
     </row>
@@ -14519,7 +14519,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>0.6565103601651208</t>
+          <t>0.4671891669093462</t>
         </is>
       </c>
     </row>
@@ -14536,7 +14536,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>0.7792595439685595</t>
+          <t>0.5394750961455853</t>
         </is>
       </c>
     </row>
@@ -14553,7 +14553,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>0.7792595439685595</t>
+          <t>0.5394750961455853</t>
         </is>
       </c>
     </row>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>0.7642039498928617</t>
+          <t>0.5349454173810527</t>
         </is>
       </c>
     </row>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>0.5943956676240301</t>
+          <t>0.37385078865978627</t>
         </is>
       </c>
     </row>
@@ -14604,7 +14604,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>0.7138672085502374</t>
+          <t>0.3313570592086957</t>
         </is>
       </c>
     </row>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>0.6667213520416455</t>
+          <t>0.35974690506436063</t>
         </is>
       </c>
     </row>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>0.3473887699575347</t>
+          <t>0.28085248183649003</t>
         </is>
       </c>
     </row>
@@ -14655,7 +14655,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>0.5998892071521699</t>
+          <t>0.4018678261947638</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>0.3810926944988946</t>
+          <t>0.3601549364946075</t>
         </is>
       </c>
     </row>
@@ -14689,7 +14689,7 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>0.9156850719552424</t>
+          <t>0.9090909090909087</t>
         </is>
       </c>
     </row>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>0.5814703136567769</t>
+          <t>0.5424648208000653</t>
         </is>
       </c>
     </row>
@@ -14723,7 +14723,7 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>0.36277596329720146</t>
+          <t>0.30054016298402125</t>
         </is>
       </c>
     </row>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>0.7372038858376462</t>
+          <t>0.6352518378348373</t>
         </is>
       </c>
     </row>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>0.7473916042214731</t>
+          <t>0.7806480805817444</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>0.8116993396258765</t>
+          <t>0.7176107193129794</t>
         </is>
       </c>
     </row>
@@ -14791,7 +14791,7 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>0.6858154656525228</t>
+          <t>0.7227998614925449</t>
         </is>
       </c>
     </row>
@@ -14808,7 +14808,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>0.8152975655059423</t>
+          <t>0.5394750961455853</t>
         </is>
       </c>
     </row>
@@ -14825,7 +14825,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>0.8903484540676481</t>
+          <t>0.7176107193129794</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>0.9483085247724613</t>
+          <t>0.7176107193129794</t>
         </is>
       </c>
     </row>
@@ -14859,7 +14859,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>0.3825860929196665</t>
+          <t>0.35511294207295513</t>
         </is>
       </c>
     </row>
@@ -14876,7 +14876,7 @@
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>0.39308015547315306</t>
+          <t>0.48224120153454747</t>
         </is>
       </c>
     </row>
@@ -14893,7 +14893,7 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>0.4174525357228982</t>
+          <t>0.39404244146696793</t>
         </is>
       </c>
     </row>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>0.35630988593765284</t>
+          <t>0.45074145636668883</t>
         </is>
       </c>
     </row>
@@ -14927,7 +14927,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>0.3477783984578286</t>
+          <t>0.2904336506587351</t>
         </is>
       </c>
     </row>
@@ -14944,7 +14944,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>0.44784557471932773</t>
+          <t>0.538000517892964</t>
         </is>
       </c>
     </row>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>0.4183011129200479</t>
+          <t>0.3793310750001994</t>
         </is>
       </c>
     </row>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>0.9340768271178619</t>
+          <t>0.8698195649472922</t>
         </is>
       </c>
     </row>
@@ -14995,7 +14995,7 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>0.5503073333297466</t>
+          <t>0.35616023878991876</t>
         </is>
       </c>
     </row>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>0.9425223664137268</t>
+          <t>0.691539318187065</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.9090909090909087</t>
         </is>
       </c>
     </row>
@@ -15046,7 +15046,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>0.9156850719552424</t>
+          <t>0.8181818181818176</t>
         </is>
       </c>
     </row>
@@ -15063,7 +15063,7 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>0.6415123997208447</t>
+          <t>0.3750359781396536</t>
         </is>
       </c>
     </row>
@@ -15080,7 +15080,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>0.9045801517222475</t>
+          <t>0.6044740060961418</t>
         </is>
       </c>
     </row>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.7955349449465988</t>
         </is>
       </c>
     </row>
@@ -15114,7 +15114,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.7955349449465988</t>
         </is>
       </c>
     </row>
@@ -15131,7 +15131,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>0.5715432459888516</t>
+          <t>0.35511294207295513</t>
         </is>
       </c>
     </row>
@@ -15148,7 +15148,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>0.5694956703583551</t>
+          <t>0.3853614108258934</t>
         </is>
       </c>
     </row>
@@ -15165,7 +15165,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>0.6154587809277017</t>
+          <t>0.3379380763696062</t>
         </is>
       </c>
     </row>
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>0.5620042913571779</t>
+          <t>0.3181818181818176</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>0.42770828137352684</t>
+          <t>0.31599575119442</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>0.49177207588498895</t>
+          <t>0.41145968847318215</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>0.4219880495235412</t>
+          <t>0.3139484599401525</t>
         </is>
       </c>
     </row>
@@ -15250,7 +15250,7 @@
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>0.40605371407846375</t>
+          <t>0.35150148611071896</t>
         </is>
       </c>
     </row>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>0.7495514109030879</t>
+          <t>0.622361297773206</t>
         </is>
       </c>
     </row>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>0.817487004083267</t>
+          <t>0.8747778408107509</t>
         </is>
       </c>
     </row>
@@ -15301,7 +15301,7 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>0.7521906577609695</t>
+          <t>0.5129848652754715</t>
         </is>
       </c>
     </row>
@@ -15318,7 +15318,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>0.4026207845221839</t>
+          <t>0.28801354180883354</t>
         </is>
       </c>
     </row>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>0.7703691820105993</t>
+          <t>0.5773245316887811</t>
         </is>
       </c>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>0.7495514109030879</t>
+          <t>0.5442925632255495</t>
         </is>
       </c>
     </row>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>0.7495514109030879</t>
+          <t>0.5442925632255495</t>
         </is>
       </c>
     </row>
@@ -15386,7 +15386,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>0.5105544535606018</t>
+          <t>0.3690162309782803</t>
         </is>
       </c>
     </row>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>0.4019188506971638</t>
+          <t>0.3328376824688722</t>
         </is>
       </c>
     </row>
@@ -15420,7 +15420,7 @@
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>0.5487083623079247</t>
+          <t>0.36315200507917744</t>
         </is>
       </c>
     </row>
@@ -15437,7 +15437,7 @@
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>0.47636259571133543</t>
+          <t>0.23835559345881627</t>
         </is>
       </c>
     </row>
@@ -15454,7 +15454,7 @@
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>0.3494303868617336</t>
+          <t>0.1457999419469777</t>
         </is>
       </c>
     </row>
@@ -15471,7 +15471,7 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>0.5131668748329558</t>
+          <t>0.42941017497324335</t>
         </is>
       </c>
     </row>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>0.2665360567681437</t>
+          <t>0.31112012295349545</t>
         </is>
       </c>
     </row>
@@ -15505,7 +15505,7 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>0.35228945072651</t>
+          <t>0.26503006417710606</t>
         </is>
       </c>
     </row>
@@ -15522,7 +15522,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>0.6640493282686909</t>
+          <t>0.36086048193714626</t>
         </is>
       </c>
     </row>
@@ -15539,7 +15539,7 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>0.6323032965226588</t>
+          <t>0.36765045118362477</t>
         </is>
       </c>
     </row>
@@ -15556,7 +15556,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>0.38269285380192286</t>
+          <t>0.25344373660453184</t>
         </is>
       </c>
     </row>
@@ -15573,7 +15573,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>0.40311100702533</t>
+          <t>0.26464661369435943</t>
         </is>
       </c>
     </row>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>0.34930389119462474</t>
+          <t>0.26464661369435943</t>
         </is>
       </c>
     </row>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>0.42337657555433356</t>
+          <t>0.26464661369435943</t>
         </is>
       </c>
     </row>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>0.36803068593488697</t>
+          <t>0.1923194105805585</t>
         </is>
       </c>
     </row>
@@ -15641,7 +15641,7 @@
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>0.37153660458225557</t>
+          <t>0.295030651065654</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>0.3996024176010812</t>
+          <t>0.2165673556346486</t>
         </is>
       </c>
     </row>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>0.3622175120720811</t>
+          <t>0.27452891578982874</t>
         </is>
       </c>
     </row>
@@ -15692,7 +15692,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>0.27416960669424245</t>
+          <t>0.1780908002492842</t>
         </is>
       </c>
     </row>
@@ -15709,7 +15709,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>0.4353828192990374</t>
+          <t>0.2165673556346486</t>
         </is>
       </c>
     </row>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>0.5004537921507615</t>
+          <t>0.3804701363500767</t>
         </is>
       </c>
     </row>
@@ -15743,7 +15743,7 @@
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.7013261952528939</t>
         </is>
       </c>
     </row>
@@ -15760,7 +15760,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.8344497155649022</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>0.8014678364619716</t>
+          <t>0.6040309358633749</t>
         </is>
       </c>
     </row>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>0.934076827117862</t>
+          <t>0.8121667612161266</t>
         </is>
       </c>
     </row>
@@ -15811,7 +15811,7 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.8217942311512769</t>
         </is>
       </c>
     </row>
@@ -15828,7 +15828,7 @@
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.8217942311512769</t>
         </is>
       </c>
     </row>
@@ -15845,7 +15845,7 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>0.522809933503755</t>
+          <t>0.2857263918249152</t>
         </is>
       </c>
     </row>
@@ -15862,7 +15862,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>0.3522840139799054</t>
+          <t>0.34028144451823017</t>
         </is>
       </c>
     </row>
@@ -15879,7 +15879,7 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>0.5483399343392193</t>
+          <t>0.4394969869215132</t>
         </is>
       </c>
     </row>
@@ -15896,7 +15896,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>0.47372358991636565</t>
+          <t>0.3122923900760036</t>
         </is>
       </c>
     </row>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>0.4471742512810563</t>
+          <t>0.2918968298033054</t>
         </is>
       </c>
     </row>
@@ -15930,7 +15930,7 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>0.44578885501758625</t>
+          <t>0.4394969869215132</t>
         </is>
       </c>
     </row>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>0.4997466087455868</t>
+          <t>0.36804804141244774</t>
         </is>
       </c>
     </row>
@@ -15964,7 +15964,7 @@
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.8181818181818177</t>
         </is>
       </c>
     </row>
@@ -15981,7 +15981,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>0.698978029656733</t>
+          <t>0.4798218853481077</t>
         </is>
       </c>
     </row>
@@ -15998,7 +15998,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>0.9340768271178619</t>
+          <t>0.6869446020268782</t>
         </is>
       </c>
     </row>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.7527139881537211</t>
         </is>
       </c>
     </row>
@@ -16032,7 +16032,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.7834535653880486</t>
         </is>
       </c>
     </row>
@@ -16049,7 +16049,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>0.47017739160776706</t>
+          <t>0.25447734139228184</t>
         </is>
       </c>
     </row>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>0.4277718980060125</t>
+          <t>0.3112208622067364</t>
         </is>
       </c>
     </row>
@@ -16083,7 +16083,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>0.7029155270281294</t>
+          <t>0.34985949680363276</t>
         </is>
       </c>
     </row>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>0.47372358991636565</t>
+          <t>0.2624678573955816</t>
         </is>
       </c>
     </row>
@@ -16117,7 +16117,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>0.29114716854259876</t>
+          <t>0.24614391810739053</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>0.5060883604535684</t>
+          <t>0.36903047532984845</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>0.3872805148151406</t>
+          <t>0.23979523746534442</t>
         </is>
       </c>
     </row>
@@ -16168,7 +16168,7 @@
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>0.6430516235991681</t>
+          <t>0.5224003345630388</t>
         </is>
       </c>
     </row>
@@ -16185,7 +16185,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>0.9190854481162105</t>
+          <t>0.7795400338523438</t>
         </is>
       </c>
     </row>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.9999999999999996</t>
         </is>
       </c>
     </row>
@@ -16219,7 +16219,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.9999999999999996</t>
         </is>
       </c>
     </row>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>0.39178274164832066</t>
+          <t>0.43247412727545337</t>
         </is>
       </c>
     </row>
@@ -16253,7 +16253,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>0.3062821080641511</t>
+          <t>0.3853614108258934</t>
         </is>
       </c>
     </row>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>0.4929324319859154</t>
+          <t>0.3294822933436382</t>
         </is>
       </c>
     </row>
@@ -16287,7 +16287,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>0.3845113849863816</t>
+          <t>0.3181818181818176</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>0.2981611106030612</t>
+          <t>0.26438490806685266</t>
         </is>
       </c>
     </row>
@@ -16321,7 +16321,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>0.47026710937760235</t>
+          <t>0.3594030053946979</t>
         </is>
       </c>
     </row>
@@ -16338,7 +16338,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>0.41457713114803335</t>
+          <t>0.23979523746534442</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>0.6293585323087786</t>
+          <t>0.46597245627934347</t>
         </is>
       </c>
     </row>
@@ -16372,7 +16372,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>0.6915799630064797</t>
+          <t>0.7058077982476351</t>
         </is>
       </c>
     </row>
@@ -16389,7 +16389,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>0.7306508931782006</t>
+          <t>0.7375130663813257</t>
         </is>
       </c>
     </row>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>0.45789407293545287</t>
+          <t>0.34147452236896836</t>
         </is>
       </c>
     </row>
@@ -16423,7 +16423,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>0.36879821436859317</t>
+          <t>0.2318815036897038</t>
         </is>
       </c>
     </row>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>0.40733046544895657</t>
+          <t>0.4394969869215132</t>
         </is>
       </c>
     </row>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>0.40418981905339163</t>
+          <t>0.24475274224955926</t>
         </is>
       </c>
     </row>
@@ -16474,7 +16474,7 @@
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>0.3765001858869249</t>
+          <t>0.3281416048044844</t>
         </is>
       </c>
     </row>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>0.49191655770842246</t>
+          <t>0.4394969869215132</t>
         </is>
       </c>
     </row>
@@ -16508,7 +16508,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>0.6268176385167491</t>
+          <t>0.5140873684634881</t>
         </is>
       </c>
     </row>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.9090909090909087</t>
         </is>
       </c>
     </row>
@@ -16542,7 +16542,7 @@
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.9090909090909087</t>
         </is>
       </c>
     </row>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>0.39856457674055584</t>
+          <t>0.3494936271144659</t>
         </is>
       </c>
     </row>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>0.2796482526266743</t>
+          <t>0.3445151779434183</t>
         </is>
       </c>
     </row>
@@ -16593,7 +16593,7 @@
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>0.4774785046410294</t>
+          <t>0.4114596884731822</t>
         </is>
       </c>
     </row>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>0.339233585793611</t>
+          <t>0.34147452236896847</t>
         </is>
       </c>
     </row>
@@ -16627,7 +16627,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>0.31571105829482743</t>
+          <t>0.3619467860520613</t>
         </is>
       </c>
     </row>
@@ -16644,7 +16644,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>0.5133633663215261</t>
+          <t>0.4114596884731822</t>
         </is>
       </c>
     </row>
@@ -16661,7 +16661,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>0.4905915442169744</t>
+          <t>0.3060173381759994</t>
         </is>
       </c>
     </row>
@@ -16678,7 +16678,7 @@
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.9999999999999996</t>
         </is>
       </c>
     </row>
@@ -16695,7 +16695,7 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>0.49886223957897563</t>
+          <t>0.43247412727545337</t>
         </is>
       </c>
     </row>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>0.2660694999205808</t>
+          <t>0.3853614108258934</t>
         </is>
       </c>
     </row>
@@ -16729,7 +16729,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>0.5126525674649292</t>
+          <t>0.4442970393380977</t>
         </is>
       </c>
     </row>
@@ -16746,7 +16746,7 @@
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>0.39625281978992544</t>
+          <t>0.3181818181818176</t>
         </is>
       </c>
     </row>
@@ -16763,7 +16763,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>0.31403152086999003</t>
+          <t>0.37346814573636616</t>
         </is>
       </c>
     </row>
@@ -16780,7 +16780,7 @@
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>0.5487540105642498</t>
+          <t>0.4442970393380977</t>
         </is>
       </c>
     </row>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>0.5450687162046315</t>
+          <t>0.37948681519606997</t>
         </is>
       </c>
     </row>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>0.41688894173905355</t>
+          <t>0.43247412727545337</t>
         </is>
       </c>
     </row>
@@ -16831,7 +16831,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>0.2660694999205808</t>
+          <t>0.3853614108258934</t>
         </is>
       </c>
     </row>
@@ -16848,7 +16848,7 @@
       </c>
       <c r="C966" t="inlineStr">
         <is>
-          <t>0.5317930024070758</t>
+          <t>0.3836227252527314</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>0.3845113849863816</t>
+          <t>0.3181818181818176</t>
         </is>
       </c>
     </row>
@@ -16882,7 +16882,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>0.36370050938568116</t>
+          <t>0.32936478636302646</t>
         </is>
       </c>
     </row>
@@ -16899,7 +16899,7 @@
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>0.5010673191136287</t>
+          <t>0.3836227252527314</t>
         </is>
       </c>
     </row>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>0.6098517876332177</t>
+          <t>0.3640442183401879</t>
         </is>
       </c>
     </row>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>0.8165219710173579</t>
+          <t>0.6226657212700846</t>
         </is>
       </c>
     </row>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>0.7148881462351875</t>
+          <t>0.36004976667337935</t>
         </is>
       </c>
     </row>
@@ -16967,7 +16967,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>0.9983636725938129</t>
+          <t>0.8061969726930833</t>
         </is>
       </c>
     </row>
@@ -16984,7 +16984,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>0.18646802038688798</t>
+          <t>0.2138678466546262</t>
         </is>
       </c>
     </row>
@@ -17001,7 +17001,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>0.6041184781729552</t>
+          <t>0.36004976667337935</t>
         </is>
       </c>
     </row>
@@ -17018,7 +17018,7 @@
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>0.2900351930497636</t>
+          <t>0.27317436401671363</t>
         </is>
       </c>
     </row>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>0.48289161707715866</t>
+          <t>0.19320106163716755</t>
         </is>
       </c>
     </row>
@@ -17052,7 +17052,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>0.9998182469603427</t>
+          <t>0.998509098917632</t>
         </is>
       </c>
     </row>
@@ -17069,7 +17069,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>0.42603399094958966</t>
+          <t>0.2527570562917229</t>
         </is>
       </c>
     </row>
@@ -17086,7 +17086,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>0.36251223440722047</t>
+          <t>0.19320106163716755</t>
         </is>
       </c>
     </row>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>0.3483827919937081</t>
+          <t>0.3082474370421201</t>
         </is>
       </c>
     </row>
@@ -17120,7 +17120,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>0.8175072881213616</t>
+          <t>0.4808797773934798</t>
         </is>
       </c>
     </row>
@@ -17137,7 +17137,7 @@
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>0.20894377738414507</t>
+          <t>0.14334637218747343</t>
         </is>
       </c>
     </row>
@@ -17154,7 +17154,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>0.663963071979175</t>
+          <t>0.529181152383134</t>
         </is>
       </c>
     </row>
@@ -17171,7 +17171,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>0.2644358860625594</t>
+          <t>0.2725390430958687</t>
         </is>
       </c>
     </row>
@@ -17188,7 +17188,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>0.4416525341971574</t>
+          <t>0.2683755102288626</t>
         </is>
       </c>
     </row>
@@ -17205,7 +17205,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>0.5997663863335141</t>
+          <t>0.44106527285765307</t>
         </is>
       </c>
     </row>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="C988" t="inlineStr">
         <is>
-          <t>0.346280788629154</t>
+          <t>0.25452505464548986</t>
         </is>
       </c>
     </row>
@@ -17239,7 +17239,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>0.2578035345308588</t>
+          <t>0.14334637218747343</t>
         </is>
       </c>
     </row>
@@ -17256,7 +17256,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>0.22564652359495185</t>
+          <t>0.23514000819026454</t>
         </is>
       </c>
     </row>
@@ -17273,11 +17273,11 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>0.3067214013209377</t>
+          <t>0.2775725935865046</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>